--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N100_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>1.714653876094201</v>
       </c>
       <c r="E2" t="n">
-        <v>28.21399101623554</v>
+        <v>26.0671236307658</v>
       </c>
       <c r="F2" t="n">
-        <v>39.06514014548124</v>
+        <v>36.43915107695018</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>3.554051340468237</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.404705169756935</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.0671236307658</v>
+      </c>
+      <c r="F3" t="n">
+        <v>36.43915107695018</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0035F0002T0006Z000C1N100.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>57.64543282646851</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>79.84493416705668</v>
       </c>
-      <c r="E3" t="n">
-        <v>28.21399101623554</v>
-      </c>
-      <c r="F3" t="n">
-        <v>39.06514014548124</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>26.0671236307658</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36.43915107695018</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.217450793997424</v>
+        <v>0.1978357540245814</v>
       </c>
       <c r="D2" t="n">
-        <v>1.714653876094201</v>
+        <v>0.2786312548653077</v>
       </c>
       <c r="E2" t="n">
-        <v>26.0671236307658</v>
+        <v>4.235907589999443</v>
       </c>
       <c r="F2" t="n">
-        <v>36.43915107695018</v>
+        <v>5.921362050004404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.554051340468237</v>
+        <v>0.5775333428260886</v>
       </c>
       <c r="D3" t="n">
-        <v>3.404705169756935</v>
+        <v>0.553264590085502</v>
       </c>
       <c r="E3" t="n">
-        <v>26.0671236307658</v>
+        <v>4.235907589999443</v>
       </c>
       <c r="F3" t="n">
-        <v>36.43915107695018</v>
+        <v>5.921362050004404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.64543282646851</v>
+        <v>9.367382834301132</v>
       </c>
       <c r="D4" t="n">
-        <v>79.84493416705668</v>
+        <v>12.97480180214671</v>
       </c>
       <c r="E4" t="n">
-        <v>26.0671236307658</v>
+        <v>4.235907589999443</v>
       </c>
       <c r="F4" t="n">
-        <v>36.43915107695018</v>
+        <v>5.921362050004404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
